--- a/resource/groundTruths/CF_M08_ground_truth.xlsx
+++ b/resource/groundTruths/CF_M08_ground_truth.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59067528-0BE6-8D49-9C01-F648A062360A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D595838F-80EE-5447-A511-50DE1C751C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="940" yWindow="1240" windowWidth="27900" windowHeight="16380" xr2:uid="{2BF46529-C427-DF4D-A3C9-B1BEAE83C956}"/>
   </bookViews>
@@ -1339,7 +1339,7 @@
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H21" s="5">
         <v>31</v>
@@ -1387,7 +1387,7 @@
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H23" s="5">
         <v>32</v>

--- a/resource/groundTruths/CF_M08_ground_truth.xlsx
+++ b/resource/groundTruths/CF_M08_ground_truth.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D595838F-80EE-5447-A511-50DE1C751C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511E7BC6-FEF8-6B46-B44E-1387D502FE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="940" yWindow="1240" windowWidth="27900" windowHeight="16380" xr2:uid="{2BF46529-C427-DF4D-A3C9-B1BEAE83C956}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="99">
   <si>
     <t>CF_M08</t>
   </si>
@@ -76,10 +76,6 @@
     <t>CF_M08_R06</t>
   </si>
   <si>
-    <t>The system must be able to save all the images of all the products and users of the
-system.</t>
-  </si>
-  <si>
     <t>CF_M08_R07a</t>
   </si>
   <si>
@@ -95,17 +91,9 @@
     <t>CF_M08_R08</t>
   </si>
   <si>
-    <t>A company must have access to the system dashboard to be able to use the different ones
-internal functionalities and additional information (statistics, values, etc.).</t>
-  </si>
-  <si>
     <t>CF_M08_R09</t>
   </si>
   <si>
-    <t>A company must be able to register a product and have it visible on its profile/page
-public.</t>
-  </si>
-  <si>
     <t>CF_M08_R10</t>
   </si>
   <si>
@@ -115,29 +103,13 @@
     <t>CF_M08_R11</t>
   </si>
   <si>
-    <t>A user must be able to return a product registered in a company through the
-use of its routes.</t>
-  </si>
-  <si>
     <t>CF_M08_R12</t>
   </si>
   <si>
-    <t>Every product must have a predetermined route in which the user returns it
-on his own account and with his own means.</t>
-  </si>
-  <si>
     <t>CF_M08_R13</t>
   </si>
   <si>
-    <t>Every route must have an associated budget (can be 0) which the user must
-be able to pay using the system when returning the product.</t>
-  </si>
-  <si>
     <t>CF_M08_R14</t>
-  </si>
-  <si>
-    <t>The system must have a membership system/plans for companies that want to
-have certain advantages.</t>
   </si>
   <si>
     <t>CF_M08_R15</t>
@@ -174,44 +146,24 @@
     <t>CF_M08_R17</t>
   </si>
   <si>
-    <t>The user interface must be intuitive and
-easy to use for non-technical users.</t>
-  </si>
-  <si>
     <t>11a. Ease of Use Requirements</t>
   </si>
   <si>
     <t>CF_M08_R18</t>
   </si>
   <si>
-    <t>Performance of usability tests with at least 10 representative users, achieving
-a minimum satisfaction score of 8/10.</t>
-  </si>
-  <si>
     <t>CF_M08_R19</t>
   </si>
   <si>
-    <t>The system must protect the information of
-the users through the following authentication</t>
-  </si>
-  <si>
     <t>15c. Privacy Requirements</t>
   </si>
   <si>
     <t>CF_M08_R20</t>
   </si>
   <si>
-    <t xml:space="preserve"> The system must pass security audits
-data without critical vulnerabilities.</t>
-  </si>
-  <si>
     <t>CF_M08_R21a</t>
   </si>
   <si>
-    <t>The system must be able to recover from failures
-in less than 1 hour.</t>
-  </si>
-  <si>
     <t>CF_M08_R21b</t>
   </si>
   <si>
@@ -245,27 +197,15 @@
     <t>CF_M08_R24a</t>
   </si>
   <si>
-    <t>The system must be compatible with the
-most common web browsers.</t>
-  </si>
-  <si>
     <t>14c. Adaptability requirements</t>
   </si>
   <si>
     <t>CF_M08_R24b</t>
   </si>
   <si>
-    <t>The system must be compatible with the
-most common mobile devices.</t>
-  </si>
-  <si>
     <t>CF_M08_R25a</t>
   </si>
   <si>
-    <t>Evidence of compatibility that they demonstrate functionality in the main browsers (Chrome, Firefox,
-Safari, Edge).</t>
-  </si>
-  <si>
     <t>CF_M08_R25b</t>
   </si>
   <si>
@@ -275,47 +215,24 @@
     <t>CF_M08_R26</t>
   </si>
   <si>
-    <t>The system must be scalable to handle
-an increase in the number of users and volume of data</t>
-  </si>
-  <si>
     <t>12 g. Scalability and Growth Requirements</t>
   </si>
   <si>
     <t>CF_M08_R27</t>
   </si>
   <si>
-    <t>Capacity to increase the resources of the
-server and maintain performance with a
-50% increase in workload.</t>
-  </si>
-  <si>
     <t>CF_M08_R28a</t>
   </si>
   <si>
-    <t>The products of a company
-they can only be edited and accessible by that
-company.</t>
-  </si>
-  <si>
     <t>15a. Access Requirement</t>
   </si>
   <si>
     <t>CF_M08_R28b</t>
   </si>
   <si>
-    <t>The routes of a company
-they can only be edited and accessible by that
-company.</t>
-  </si>
-  <si>
     <t>CF_M08_R28c</t>
   </si>
   <si>
-    <t>The profile of a company can only be edited and accessible by that
-company.</t>
-  </si>
-  <si>
     <t>CF_M08_R29</t>
   </si>
   <si>
@@ -350,6 +267,72 @@
   </si>
   <si>
     <t>Applied Fixes</t>
+  </si>
+  <si>
+    <t>A user must be able to return a product registered in a company throug the use of its routes.</t>
+  </si>
+  <si>
+    <t>The system must be able to save all the images of all the products and users of the system.</t>
+  </si>
+  <si>
+    <t>A company must have access to the system dashboard to be able to use the different ones internal functionalities and additional information (statistics, values, etc.).</t>
+  </si>
+  <si>
+    <t>A company must be able to register a product and have it visible on its profile/page public.</t>
+  </si>
+  <si>
+    <t>Every product must have a predetermined route in which the user returns it on his own account and with his own means.</t>
+  </si>
+  <si>
+    <t>Every route must have an associated budget (can be 0) which the user must be able to pay using the system when returning the product.</t>
+  </si>
+  <si>
+    <t>The system must have a membership system/plans for companies that want to have certain advantages.</t>
+  </si>
+  <si>
+    <t>The user interface must be intuitive and easy to use for non-technical users.</t>
+  </si>
+  <si>
+    <t>Performance of usability tests with at least 10 representative users, achieving a minimum satisfaction score of 8/10.</t>
+  </si>
+  <si>
+    <t>The system must protect the information of the users through the following authentication.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The system must pass security audits data without critical vulnerabilities.</t>
+  </si>
+  <si>
+    <t>The system must be able to recover from failures in less than 1 hour.</t>
+  </si>
+  <si>
+    <t>The system must be compatible with the most common web browsers.</t>
+  </si>
+  <si>
+    <t>The system must be compatible with the most common mobile devices.</t>
+  </si>
+  <si>
+    <t>Evidence of compatibility that they demonstrate functionality in the main browsers (Chrome, Firefox, Safari, Edge).</t>
+  </si>
+  <si>
+    <t>The system must be scalable to handle an increase in the number of users and volume of data</t>
+  </si>
+  <si>
+    <t>Capacity to increase the resources of the server and maintain performance with a 50% increase in workload.</t>
+  </si>
+  <si>
+    <t>The products of a company can only be edited and accessible by that company.</t>
+  </si>
+  <si>
+    <t>The routes of a company can only be edited and accessible by that company.</t>
+  </si>
+  <si>
+    <t>The profile of a company can only be edited and accessible by that company.</t>
+  </si>
+  <si>
+    <t>Split</t>
+  </si>
+  <si>
+    <t>Classification changed</t>
   </si>
 </sst>
 </file>
@@ -885,31 +868,31 @@
   <sheetData>
     <row r="1" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -1025,7 +1008,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>3</v>
@@ -1043,10 +1026,10 @@
         <v>0</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>3</v>
@@ -1057,17 +1040,19 @@
       <c r="H8" s="2">
         <v>30</v>
       </c>
-      <c r="I8" s="3"/>
+      <c r="I8" s="3" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>17</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>3</v>
@@ -1078,17 +1063,19 @@
       <c r="H9" s="5">
         <v>30</v>
       </c>
-      <c r="I9" s="6"/>
+      <c r="I9" s="6" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>3</v>
@@ -1106,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>3</v>
@@ -1127,10 +1114,10 @@
         <v>0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>3</v>
@@ -1143,15 +1130,15 @@
       </c>
       <c r="I12" s="3"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="120" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>77</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>3</v>
@@ -1164,15 +1151,15 @@
       </c>
       <c r="I13" s="6"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="150" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>3</v>
@@ -1185,15 +1172,15 @@
       </c>
       <c r="I14" s="3"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="165" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>82</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>3</v>
@@ -1206,15 +1193,15 @@
       </c>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="120" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>83</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>3</v>
@@ -1232,19 +1219,19 @@
         <v>0</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G17" s="9"/>
       <c r="H17" s="5">
@@ -1257,65 +1244,69 @@
         <v>0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H18" s="2">
         <v>31</v>
       </c>
-      <c r="I18" s="7"/>
+      <c r="I18" s="7" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H19" s="5">
         <v>31</v>
       </c>
-      <c r="I19" s="6"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I19" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="105" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>84</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2">
@@ -1323,47 +1314,47 @@
       </c>
       <c r="I20" s="3"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="150" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>46</v>
+        <v>37</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>85</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H21" s="5">
         <v>31</v>
       </c>
       <c r="I21" s="6"/>
     </row>
-    <row r="22" spans="1:9" ht="120" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="135" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2">
@@ -1376,18 +1367,18 @@
         <v>0</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="H23" s="5">
         <v>32</v>
@@ -1399,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
@@ -1413,20 +1404,22 @@
       <c r="H24" s="2">
         <v>32</v>
       </c>
-      <c r="I24" s="3"/>
+      <c r="I24" s="3" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -1434,20 +1427,22 @@
       <c r="H25" s="5">
         <v>32</v>
       </c>
-      <c r="I25" s="6"/>
+      <c r="I25" s="6" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
@@ -1462,13 +1457,13 @@
         <v>0</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -1476,20 +1471,22 @@
       <c r="H27" s="5">
         <v>32</v>
       </c>
-      <c r="I27" s="6"/>
+      <c r="I27" s="6" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
@@ -1497,25 +1494,27 @@
       <c r="H28" s="2">
         <v>32</v>
       </c>
-      <c r="I28" s="3"/>
+      <c r="I28" s="3" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="29" spans="1:9" ht="91" x14ac:dyDescent="0.2">
       <c r="A29" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E29" s="14"/>
       <c r="F29" s="14"/>
       <c r="G29" s="14" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="H29" s="5">
         <v>32</v>
@@ -1527,19 +1526,19 @@
         <v>0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2">
@@ -1552,19 +1551,19 @@
         <v>0</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5">
@@ -1577,65 +1576,69 @@
         <v>0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H32" s="2">
         <v>33</v>
       </c>
-      <c r="I32" s="3"/>
+      <c r="I32" s="3" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="H33" s="5">
         <v>33</v>
       </c>
-      <c r="I33" s="6"/>
+      <c r="I33" s="6" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2">
@@ -1648,18 +1651,18 @@
         <v>0</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
       <c r="G35" s="5" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="H35" s="5">
         <v>33</v>
@@ -1671,88 +1674,94 @@
         <v>0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2">
         <v>33</v>
       </c>
-      <c r="I36" s="3"/>
+      <c r="I36" s="3" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G37" s="16"/>
       <c r="H37" s="12">
         <v>33</v>
       </c>
-      <c r="I37" s="6"/>
+      <c r="I37" s="6" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2">
         <v>33</v>
       </c>
-      <c r="I38" s="3"/>
+      <c r="I38" s="3" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
@@ -1760,7 +1769,9 @@
       <c r="H39" s="5">
         <v>31</v>
       </c>
-      <c r="I39" s="6"/>
+      <c r="I39" s="6" t="s">
+        <v>98</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/resource/groundTruths/CF_M08_ground_truth.xlsx
+++ b/resource/groundTruths/CF_M08_ground_truth.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511E7BC6-FEF8-6B46-B44E-1387D502FE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{312BEA32-3C6F-744E-AE8E-13920234F41D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="940" yWindow="1240" windowWidth="27900" windowHeight="16380" xr2:uid="{2BF46529-C427-DF4D-A3C9-B1BEAE83C956}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{2BF46529-C427-DF4D-A3C9-B1BEAE83C956}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="102">
   <si>
     <t>CF_M08</t>
   </si>
@@ -121,10 +121,6 @@
     <t>QR</t>
   </si>
   <si>
-    <t>11b. Personalization and Internal Requirements
-nationalization</t>
-  </si>
-  <si>
     <t>Volere</t>
   </si>
   <si>
@@ -167,172 +163,185 @@
     <t>CF_M08_R21b</t>
   </si>
   <si>
-    <t>Uptime monitoring that demonstrates 99.9% uptime.</t>
-  </si>
-  <si>
-    <t>CF_M08_R21c</t>
-  </si>
-  <si>
     <t>Disaster recovery testing that meets the specified recovery time.</t>
   </si>
   <si>
     <t>CF_M08_R22a</t>
   </si>
   <si>
+    <t>CF_M08_R22b</t>
+  </si>
+  <si>
+    <t>Complete and updated documentation</t>
+  </si>
+  <si>
+    <t>Average implementation time of updates and error fixes no more than 2 hours.</t>
+  </si>
+  <si>
+    <t>14c. Adaptability requirements</t>
+  </si>
+  <si>
+    <t>CF_M08_R25a</t>
+  </si>
+  <si>
+    <t>CF_M08_R25b</t>
+  </si>
+  <si>
+    <t>CF_M08_R26</t>
+  </si>
+  <si>
+    <t>12 g. Scalability and Growth Requirements</t>
+  </si>
+  <si>
+    <t>CF_M08_R27</t>
+  </si>
+  <si>
+    <t>15a. Access Requirement</t>
+  </si>
+  <si>
+    <t>The system should have three different membership plans: free, basic and premium.</t>
+  </si>
+  <si>
+    <t>Constraint</t>
+  </si>
+  <si>
+    <t>Document ID</t>
+  </si>
+  <si>
+    <t>Requirement ID</t>
+  </si>
+  <si>
+    <t>Requirement</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>Categorization</t>
+  </si>
+  <si>
+    <t>Related to</t>
+  </si>
+  <si>
+    <t>Page Number</t>
+  </si>
+  <si>
+    <t>Applied Fixes</t>
+  </si>
+  <si>
+    <t>A user must be able to return a product registered in a company throug the use of its routes.</t>
+  </si>
+  <si>
+    <t>The system must be able to save all the images of all the products and users of the system.</t>
+  </si>
+  <si>
+    <t>A company must have access to the system dashboard to be able to use the different ones internal functionalities and additional information (statistics, values, etc.).</t>
+  </si>
+  <si>
+    <t>A company must be able to register a product and have it visible on its profile/page public.</t>
+  </si>
+  <si>
+    <t>Every product must have a predetermined route in which the user returns it on his own account and with his own means.</t>
+  </si>
+  <si>
+    <t>Every route must have an associated budget (can be 0) which the user must be able to pay using the system when returning the product.</t>
+  </si>
+  <si>
+    <t>The system must have a membership system/plans for companies that want to have certain advantages.</t>
+  </si>
+  <si>
+    <t>The user interface must be intuitive and easy to use for non-technical users.</t>
+  </si>
+  <si>
+    <t>Performance of usability tests with at least 10 representative users, achieving a minimum satisfaction score of 8/10.</t>
+  </si>
+  <si>
+    <t>The system must protect the information of the users through the following authentication.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The system must pass security audits data without critical vulnerabilities.</t>
+  </si>
+  <si>
+    <t>The system must be able to recover from failures in less than 1 hour.</t>
+  </si>
+  <si>
+    <t>The system must be compatible with the most common web browsers.</t>
+  </si>
+  <si>
+    <t>The system must be compatible with the most common mobile devices.</t>
+  </si>
+  <si>
+    <t>Evidence of compatibility that they demonstrate functionality in the main browsers (Chrome, Firefox, Safari, Edge).</t>
+  </si>
+  <si>
+    <t>The system must be scalable to handle an increase in the number of users and volume of data</t>
+  </si>
+  <si>
+    <t>Capacity to increase the resources of the server and maintain performance with a 50% increase in workload.</t>
+  </si>
+  <si>
+    <t>The products of a company can only be edited and accessible by that company.</t>
+  </si>
+  <si>
+    <t>The routes of a company can only be edited and accessible by that company.</t>
+  </si>
+  <si>
+    <t>The profile of a company can only be edited and accessible by that company.</t>
+  </si>
+  <si>
+    <t>Split</t>
+  </si>
+  <si>
+    <t>Classification changed</t>
+  </si>
+  <si>
+    <t>The system must have an activity time
+of 99.9%</t>
+  </si>
+  <si>
+    <t>CF_M08_R23a</t>
+  </si>
+  <si>
+    <t>CF_M08_R23b</t>
+  </si>
+  <si>
+    <t>Evidence of compatibility that they demonstrate functionality in the mobile devices.</t>
+  </si>
+  <si>
+    <t>CF_M08_R24</t>
+  </si>
+  <si>
+    <t>CF_M08_R26a</t>
+  </si>
+  <si>
+    <t>CF_M08_R26b</t>
+  </si>
+  <si>
+    <t>CF_M08_R28</t>
+  </si>
+  <si>
+    <t>CF_M08_R29a</t>
+  </si>
+  <si>
+    <t>CF_M08_R29b</t>
+  </si>
+  <si>
+    <t>CF_M08_R29c</t>
+  </si>
+  <si>
+    <t>CF_M08_R30</t>
+  </si>
+  <si>
     <t>The system must be easy to maintain and update.</t>
   </si>
   <si>
-    <t>CF_M08_R22b</t>
-  </si>
-  <si>
-    <t>Complete and updated documentation</t>
-  </si>
-  <si>
-    <t>CF_M08_R23</t>
-  </si>
-  <si>
-    <t>Average implementation time of updates and error fixes no more than 2 hours.</t>
-  </si>
-  <si>
-    <t>CF_M08_R24a</t>
-  </si>
-  <si>
-    <t>14c. Adaptability requirements</t>
-  </si>
-  <si>
-    <t>CF_M08_R24b</t>
-  </si>
-  <si>
-    <t>CF_M08_R25a</t>
-  </si>
-  <si>
-    <t>CF_M08_R25b</t>
-  </si>
-  <si>
-    <t>Evidence of compatibility that they demonstrate functionality in the mobile devices (mobile phones and tablets).</t>
-  </si>
-  <si>
-    <t>CF_M08_R26</t>
-  </si>
-  <si>
-    <t>12 g. Scalability and Growth Requirements</t>
-  </si>
-  <si>
-    <t>CF_M08_R27</t>
-  </si>
-  <si>
-    <t>CF_M08_R28a</t>
-  </si>
-  <si>
-    <t>15a. Access Requirement</t>
-  </si>
-  <si>
-    <t>CF_M08_R28b</t>
-  </si>
-  <si>
-    <t>CF_M08_R28c</t>
-  </si>
-  <si>
-    <t>CF_M08_R29</t>
-  </si>
-  <si>
-    <t>The system should have three different membership plans: free, basic and premium.</t>
-  </si>
-  <si>
-    <t>Constraint</t>
-  </si>
-  <si>
-    <t>Document ID</t>
-  </si>
-  <si>
-    <t>Requirement ID</t>
-  </si>
-  <si>
-    <t>Requirement</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Concept</t>
-  </si>
-  <si>
-    <t>Categorization</t>
-  </si>
-  <si>
-    <t>Related to</t>
-  </si>
-  <si>
-    <t>Page Number</t>
-  </si>
-  <si>
-    <t>Applied Fixes</t>
-  </si>
-  <si>
-    <t>A user must be able to return a product registered in a company throug the use of its routes.</t>
-  </si>
-  <si>
-    <t>The system must be able to save all the images of all the products and users of the system.</t>
-  </si>
-  <si>
-    <t>A company must have access to the system dashboard to be able to use the different ones internal functionalities and additional information (statistics, values, etc.).</t>
-  </si>
-  <si>
-    <t>A company must be able to register a product and have it visible on its profile/page public.</t>
-  </si>
-  <si>
-    <t>Every product must have a predetermined route in which the user returns it on his own account and with his own means.</t>
-  </si>
-  <si>
-    <t>Every route must have an associated budget (can be 0) which the user must be able to pay using the system when returning the product.</t>
-  </si>
-  <si>
-    <t>The system must have a membership system/plans for companies that want to have certain advantages.</t>
-  </si>
-  <si>
-    <t>The user interface must be intuitive and easy to use for non-technical users.</t>
-  </si>
-  <si>
-    <t>Performance of usability tests with at least 10 representative users, achieving a minimum satisfaction score of 8/10.</t>
-  </si>
-  <si>
-    <t>The system must protect the information of the users through the following authentication.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> The system must pass security audits data without critical vulnerabilities.</t>
-  </si>
-  <si>
-    <t>The system must be able to recover from failures in less than 1 hour.</t>
-  </si>
-  <si>
-    <t>The system must be compatible with the most common web browsers.</t>
-  </si>
-  <si>
-    <t>The system must be compatible with the most common mobile devices.</t>
-  </si>
-  <si>
-    <t>Evidence of compatibility that they demonstrate functionality in the main browsers (Chrome, Firefox, Safari, Edge).</t>
-  </si>
-  <si>
-    <t>The system must be scalable to handle an increase in the number of users and volume of data</t>
-  </si>
-  <si>
-    <t>Capacity to increase the resources of the server and maintain performance with a 50% increase in workload.</t>
-  </si>
-  <si>
-    <t>The products of a company can only be edited and accessible by that company.</t>
-  </si>
-  <si>
-    <t>The routes of a company can only be edited and accessible by that company.</t>
-  </si>
-  <si>
-    <t>The profile of a company can only be edited and accessible by that company.</t>
-  </si>
-  <si>
-    <t>Split</t>
-  </si>
-  <si>
-    <t>Classification changed</t>
+    <t>Monitoring of activity time that shows an uptime of 99.9%</t>
+  </si>
+  <si>
+    <t>11b. Personalization and Internationalization Requirements</t>
   </si>
 </sst>
 </file>
@@ -497,7 +506,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -547,6 +556,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -863,36 +878,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A47BB8-5C7A-D94C-98EA-8A7C27FE3E52}">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -1008,7 +1023,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>3</v>
@@ -1041,7 +1056,7 @@
         <v>30</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -1064,7 +1079,7 @@
         <v>30</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -1075,7 +1090,7 @@
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>3</v>
@@ -1096,7 +1111,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>3</v>
@@ -1138,7 +1153,7 @@
         <v>21</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>3</v>
@@ -1159,7 +1174,7 @@
         <v>22</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>3</v>
@@ -1180,7 +1195,7 @@
         <v>23</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>3</v>
@@ -1201,7 +1216,7 @@
         <v>24</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>3</v>
@@ -1228,10 +1243,10 @@
         <v>27</v>
       </c>
       <c r="E17" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>29</v>
       </c>
       <c r="G17" s="9"/>
       <c r="H17" s="5">
@@ -1244,13 +1259,13 @@
         <v>0</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -1261,7 +1276,7 @@
         <v>31</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
@@ -1269,13 +1284,13 @@
         <v>0</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="D19" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -1286,7 +1301,7 @@
         <v>31</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="105" x14ac:dyDescent="0.2">
@@ -1294,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2">
@@ -1319,18 +1334,18 @@
         <v>0</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H21" s="5">
         <v>31</v>
@@ -1342,19 +1357,19 @@
         <v>0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2">
@@ -1367,126 +1382,132 @@
         <v>0</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H23" s="5">
         <v>32</v>
       </c>
       <c r="I23" s="6"/>
     </row>
-    <row r="24" spans="1:9" ht="90" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="2" t="s">
+    <row r="24" spans="1:9" ht="60" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5">
+        <v>32</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="90" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="C25" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2">
         <v>32</v>
       </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2">
-        <v>32</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="5" t="s">
+      <c r="I25" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="78" x14ac:dyDescent="0.2">
+      <c r="A26" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5">
-        <v>32</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>45</v>
+      <c r="C26" s="22" t="s">
+        <v>100</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H26" s="12">
         <v>32</v>
       </c>
-      <c r="I26" s="3"/>
+      <c r="I26" s="3" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" s="5" t="s">
+      <c r="A27" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H27" s="12">
         <v>32</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5">
-        <v>32</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>97</v>
+      <c r="I27" s="3" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>48</v>
+      <c r="B28" s="11" t="s">
+        <v>88</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
@@ -1495,287 +1516,325 @@
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2">
+        <v>32</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="91" x14ac:dyDescent="0.2">
+      <c r="A30" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="H30" s="5">
+        <v>32</v>
+      </c>
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2">
+        <v>33</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5">
+        <v>33</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H33" s="2">
+        <v>33</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H34" s="5">
+        <v>33</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2">
+        <v>33</v>
+      </c>
+      <c r="I35" s="3"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H36" s="5">
+        <v>33</v>
+      </c>
+      <c r="I36" s="6"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2">
+        <v>33</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A38" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G38" s="16"/>
+      <c r="H38" s="12">
+        <v>33</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="11" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" ht="91" x14ac:dyDescent="0.2">
-      <c r="A29" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="H29" s="5">
-        <v>32</v>
-      </c>
-      <c r="I29" s="6"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="C39" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2">
+      <c r="F39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2">
         <v>33</v>
       </c>
-      <c r="I30" s="3"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31" s="5" t="s">
+      <c r="I39" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5">
-        <v>33</v>
-      </c>
-      <c r="I31" s="6"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B32" s="2" t="s">
+      <c r="D40" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H32" s="2">
-        <v>33</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H33" s="5">
-        <v>33</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2">
-        <v>33</v>
-      </c>
-      <c r="I34" s="3"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H35" s="5">
-        <v>33</v>
-      </c>
-      <c r="I35" s="6"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2">
-        <v>33</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A37" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G37" s="16"/>
-      <c r="H37" s="12">
-        <v>33</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2">
-        <v>33</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A39" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5">
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5">
         <v>31</v>
       </c>
-      <c r="I39" s="6" t="s">
-        <v>98</v>
-      </c>
+      <c r="I40" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A44" s="10"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D39" xr:uid="{58CE174C-2924-FF49-B5D0-F99AA8F18BBF}">
+    <dataValidation type="list" allowBlank="1" sqref="D44 D2:D40" xr:uid="{58CE174C-2924-FF49-B5D0-F99AA8F18BBF}">
       <formula1>"FR,QR,Constraint,Criterion"</formula1>
     </dataValidation>
   </dataValidations>
